--- a/RSA analysis/All excluded subs after ibis interpolation.xlsx
+++ b/RSA analysis/All excluded subs after ibis interpolation.xlsx
@@ -428,13 +428,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sub_id (18 subs)</t>
+          <t>sub_id (17 subs)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (292) exceeds 20% of series length after interpolation(670)</t>
+          <t>Interpolated ibis count (163) exceeds 20% of series length after interpolation(541)</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (333) exceeds 20% of series length after interpolation(537)</t>
+          <t>Interpolated ibis count (79) exceeds 20% of series length after interpolation(270)</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (306) exceeds 20% of series length after interpolation(703)</t>
+          <t>Interpolated ibis count (172) exceeds 20% of series length after interpolation(568)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Session length (59.89s) is shorter than 60 sec</t>
+          <t>Session length (53.12s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Session length (53.12s) is shorter than 60 sec</t>
+          <t>Session length (59.89s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -642,18 +642,6 @@
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
         <is>
           <t>Unmatched subject</t>
         </is>
@@ -670,13 +658,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sub_id (18 subs)</t>
+          <t>sub_id (17 subs)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -705,43 +693,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (127) exceeds 20% of series length after interpolation(247)</t>
+          <t>Interpolated ibis count (40) exceeds 20% of series length after interpolation(159)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (110) exceeds 20% of series length after interpolation(335)</t>
+          <t>Session length (53.33s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (76) exceeds 20% of series length after interpolation(296)</t>
+          <t>SDRR (347.85) exceeds threshold (200)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (108) exceeds 20% of series length after interpolation(419)</t>
+          <t>SDRR (284.79) exceeds threshold (200)</t>
         </is>
       </c>
     </row>
@@ -753,26 +741,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (53) exceeds 20% of series length after interpolation(215)</t>
+          <t>SDRR (242.62) exceeds threshold (200)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Session length (53.33s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -784,7 +772,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -796,7 +784,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -808,7 +796,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -820,7 +808,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -832,7 +820,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -844,7 +832,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -856,7 +844,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -868,7 +856,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -880,22 +868,10 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
         <is>
           <t>Unmatched subject</t>
         </is>
@@ -912,13 +888,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sub_id (29 subs)</t>
+          <t>sub_id (23 subs)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -983,206 +959,206 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (55) exceeds 20% of series length after interpolation(127)</t>
+          <t>Interpolated ibis count (16) exceeds 20% of series length after interpolation(72)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (75) exceeds 20% of series length after interpolation(313)</t>
+          <t>Interpolated ibis count (73) exceeds 20% of series length after interpolation(328)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (102) exceeds 20% of series length after interpolation(357)</t>
+          <t>Interpolated ibis count (23) exceeds 20% of series length after interpolation(87)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (66) exceeds 20% of series length after interpolation(131)</t>
+          <t>Session length (33.63s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (45) exceeds 20% of series length after interpolation(182)</t>
+          <t>Session length (36.64s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Session length (54.37s) is shorter than 60 sec</t>
+          <t>Session length (57.19s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Session length (49.27s) is shorter than 60 sec</t>
+          <t>Session length (51.12s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (35) exceeds 20% of series length after interpolation(134)</t>
+          <t>Session length (15.99s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Session length (33.63s) is shorter than 60 sec</t>
+          <t>Session length (33.91s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Session length (36.64s) is shorter than 60 sec</t>
+          <t>Session length (22.91s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Session length (57.19s) is shorter than 60 sec</t>
+          <t>Session length (54.37s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Session length (51.12s) is shorter than 60 sec</t>
+          <t>Session length (49.07s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Session length (15.99s) is shorter than 60 sec</t>
+          <t>Session length (41.50s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Session length (33.91s) is shorter than 60 sec</t>
+          <t>Session length (52.73s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Session length (22.91s) is shorter than 60 sec</t>
+          <t>SDRR (339.85) exceeds threshold (200)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Session length (41.50s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Session length (52.73s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1194,82 +1170,10 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
         <is>
           <t>Unmatched subject</t>
         </is>
@@ -1286,13 +1190,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>sub_id (29 subs)</t>
+          <t>sub_id (23 subs)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1316,192 +1220,192 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (54) exceeds 20% of series length after interpolation(195)</t>
+          <t>Interpolated ibis count (20) exceeds 20% of series length after interpolation(56)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (44) exceeds 20% of series length after interpolation(204)</t>
+          <t>Session length (54.23s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (71) exceeds 20% of series length after interpolation(110)</t>
+          <t>Session length (33.84s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (60) exceeds 20% of series length after interpolation(197)</t>
+          <t>Session length (36.69s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Interpolated ibis count (51) exceeds 20% of series length after interpolation(190)</t>
+          <t>Session length (37.29s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Session length (54.23s) is shorter than 60 sec</t>
+          <t>Session length (57.19s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Session length (52.25s) is shorter than 60 sec</t>
+          <t>Session length (51.06s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Session length (33.84s) is shorter than 60 sec</t>
+          <t>Session length (34.01s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Session length (36.69s) is shorter than 60 sec</t>
+          <t>Session length (31.92s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Session length (37.29s) is shorter than 60 sec</t>
+          <t>Session length (22.52s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Session length (57.19s) is shorter than 60 sec</t>
+          <t>Session length (41.86s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Session length (51.06s) is shorter than 60 sec</t>
+          <t>Session length (52.25s) is shorter than 60 sec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Session length (34.01s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Session length (31.92s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Session length (22.52s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Session length (41.86s) is shorter than 60 sec</t>
+          <t>Unmatched subject</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1424,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1532,7 +1436,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1544,7 +1448,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1556,7 +1460,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1568,82 +1472,10 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Unmatched subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
         <is>
           <t>Unmatched subject</t>
         </is>
